--- a/mlef_pipeline/results/DCR/IO_ONLY/RWD/results.xlsx
+++ b/mlef_pipeline/results/DCR/IO_ONLY/RWD/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.64 ± 0.04</t>
+          <t>0.65 ± 0.04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.54 ± 0.04</t>
+          <t>0.60 ± 0.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71 ± 0.22</t>
+          <t>0.61 ± 0.10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.46 ± 0.21</t>
+          <t>0.62 ± 0.10</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -503,17 +503,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.61 ± 0.11</t>
+          <t>0.73 ± 0.11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F4" t="n">
